--- a/InFiRA-QA/002747-QA.xlsx
+++ b/InFiRA-QA/002747-QA.xlsx
@@ -194,10 +194,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>请计算本报告期利息偿付率。利息偿付率=EBIT/利息费用。EBIT（净利润+所得税费用+利息费用）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>请计算2022年存货周转率。存货周转率=营业成本/平均存货余额。平均存货余额=（期初存货余额+期末存货余额）/2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -238,6 +234,10 @@
   </si>
   <si>
     <t>Question</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照母公司财务报表计算2021年的利息保障倍数。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -611,7 +611,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3">
         <v>9.8699999999999996E-2</v>
@@ -878,7 +878,7 @@
         <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" s="1">
         <v>4.3099999999999996</v>
@@ -952,10 +952,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1">
-        <v>4.3099999999999996</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
         <v>2.61</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" s="10">
         <v>-4.9299999999999997E-2</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="10">
         <v>0.28489999999999999</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" s="10">
         <v>0.36280000000000001</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37" s="10">
         <v>5.5899999999999998E-2</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" s="10">
         <v>0.33850000000000002</v>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" s="10">
         <v>0.1623</v>
